--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +126,12 @@
       <color rgb="002E6B3B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color rgb="000E1B2C"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -180,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -515,11 +521,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B8862B"/>
+      </left>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -682,6 +712,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1009,7 +1054,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — OPERATIONS</t>
         </is>
@@ -1157,7 +1202,7 @@
       <c r="N8" s="56" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Block Assignment Header</t>
         </is>
@@ -1182,7 +1227,7 @@
           <t>Block ID:</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>512-OWL</t>
         </is>
@@ -1214,7 +1259,7 @@
           <t>Operator Badge:</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>4417</t>
         </is>
@@ -1246,7 +1291,7 @@
           <t>Vehicle #:</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>4177</t>
         </is>
@@ -1278,7 +1323,7 @@
           <t>Scheduled Pullout:</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>10/17/2025 22:15</t>
         </is>
@@ -1310,7 +1355,7 @@
           <t>Sign / Bid Cycle:</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Fall 2025 Sign</t>
         </is>
@@ -1337,7 +1382,7 @@
       <c r="N15" s="56" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>Block Manifest — Trip Roster</t>
         </is>
@@ -2293,7 +2338,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="63" t="inlineStr">
         <is>
           <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
         </is>
@@ -2377,7 +2422,7 @@
       <c r="N35" s="56" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>Assignment Sign-Off</t>
         </is>
@@ -2618,7 +2663,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — AUTHORIZED OWL ROUTES</t>
         </is>
@@ -2682,7 +2727,7 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>510</t>
         </is>
@@ -2714,7 +2759,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>511</t>
         </is>
@@ -2746,7 +2791,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>512</t>
         </is>
@@ -2778,7 +2823,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>514</t>
         </is>
@@ -2810,7 +2855,7 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>517</t>
         </is>
@@ -2842,7 +2887,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>519</t>
         </is>
@@ -2910,7 +2955,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — SCHEDULE NOTES</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,8 +132,14 @@
       <color rgb="000E1B2C"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +191,12 @@
         <fgColor rgb="00F5F2EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E7C6"/>
+        <bgColor rgb="00C6E7C6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -549,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -725,6 +737,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1948,22 +1963,22 @@
       </c>
       <c r="I25" s="30" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
-          <t>02:05 (SB timepoint pass) / 02:31</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="K25" s="30" t="inlineStr">
         <is>
-          <t>02:24</t>
+          <t>02:04</t>
         </is>
       </c>
       <c r="L25" s="30" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>02:04</t>
         </is>
       </c>
       <c r="M25" s="30" t="inlineStr">
@@ -2045,7 +2060,7 @@
       </c>
       <c r="N26" s="34" t="inlineStr">
         <is>
-          <t>Layover 02:37–02:45 at S. Main/Fifth</t>
+          <t>Layover 02:10–02:45 at S. Main/Fifth</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2397,12 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="35" t="inlineStr">
         <is>
-          <t>06 (SB pass, mid-loop reference)</t>
+          <t>06</t>
         </is>
       </c>
       <c r="B34" s="36" t="inlineStr">
         <is>
-          <t>Southbound reference pass at S. Main / Third</t>
+          <t>Northbound (Poplar/Rivergate Plaza → S. Main/Fifth)</t>
         </is>
       </c>
       <c r="C34" s="36" t="inlineStr">
@@ -2397,14 +2412,14 @@
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
-          <t>Northbound leg 06 passes S. Main / Third at 02:31 following downtown loop; SB reference timepoint at 02:05 is the published control point for the trip pair 05/06 turnaround</t>
+          <t>Scheduled control-point timepoint for Trip 06 northbound at S. Main / Third; matches the AVL/GPS position log, APC/farebox record, and dispatch log for the service night.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="37" t="inlineStr">
         <is>
-          <t>Timepoint reference: the 02:05 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
+          <t>Timepoint reference: the 02:05 a.m. control point at S. Main / Third is the published on-time-performance anchor for Trip 06 northbound.</t>
         </is>
       </c>
       <c r="B35" s="55" t="n"/>
@@ -2752,7 +2767,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2784,7 +2799,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F8" s="47" t="inlineStr">
+      <c r="F8" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2816,7 +2831,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2848,7 +2863,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F10" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2880,7 +2895,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F11" s="44" t="inlineStr">
+      <c r="F11" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2912,7 +2927,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F12" s="47" t="inlineStr">
+      <c r="F12" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -133,7 +133,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +185,12 @@
         <fgColor rgb="00F5F2EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCEFE0"/>
+        <bgColor rgb="FFDCEFE0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -549,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -725,6 +731,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2752,7 +2761,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2784,7 +2793,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F8" s="47" t="inlineStr">
+      <c r="F8" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2816,7 +2825,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2848,7 +2857,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F10" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2880,7 +2889,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F11" s="44" t="inlineStr">
+      <c r="F11" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2912,7 +2921,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F12" s="47" t="inlineStr">
+      <c r="F12" s="67" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
-          <t>02:05 (SB timepoint pass) / 02:31</t>
+          <t>02:31 scheduled (actual: 02:05, per incident record)</t>
         </is>
       </c>
       <c r="K25" s="30" t="inlineStr">
@@ -2347,11 +2347,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="63" t="inlineStr">
-        <is>
-          <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
-        </is>
-      </c>
+      <c r="A32" s="63" t="n"/>
       <c r="B32" s="54" t="n"/>
       <c r="C32" s="54" t="n"/>
       <c r="D32" s="54" t="n"/>
@@ -2367,55 +2363,19 @@
       <c r="N32" s="54" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>Trip #</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Scheduled Timepoint</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>06 (SB pass, mid-loop reference)</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>Southbound reference pass at S. Main / Third</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
-        <is>
-          <t>10/18/2025 02:05</t>
-        </is>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Northbound leg 06 passes S. Main / Third at 02:31 following downtown loop; SB reference timepoint at 02:05 is the published control point for the trip pair 05/06 turnaround</t>
-        </is>
-      </c>
+      <c r="A34" s="35" t="n"/>
+      <c r="B34" s="36" t="n"/>
+      <c r="C34" s="36" t="n"/>
+      <c r="D34" s="36" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
-        <is>
-          <t>Timepoint reference: the 02:05 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
-        </is>
-      </c>
+      <c r="A35" s="37" t="n"/>
       <c r="B35" s="55" t="n"/>
       <c r="C35" s="55" t="n"/>
       <c r="D35" s="55" t="n"/>
